--- a/output/pdf_financials_xlsx/INIK.xlsx
+++ b/output/pdf_financials_xlsx/INIK.xlsx
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.136619</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -9542,7 +9542,11 @@
           <t>Warrant reserve (note 5)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/INIK.xlsx
+++ b/output/pdf_financials_xlsx/INIK.xlsx
@@ -1438,25 +1438,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.469606</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.155577</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.042</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>7.795</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>7.396</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>14.565</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>11.258</v>
       </c>
     </row>
     <row r="35">
@@ -1494,25 +1494,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.469606</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.155577</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.042</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>7.795</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>7.396</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>14.565</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>11.258</v>
       </c>
     </row>
     <row r="37">
@@ -1836,19 +1836,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.205</v>
+        <v>0.163</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>8.887</v>
+        <v>1.092</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>19.014</v>
+        <v>11.618</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>17.116</v>
+        <v>2.551</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>13.019</v>
+        <v>1.761</v>
       </c>
     </row>
     <row r="49">
@@ -3971,19 +3971,19 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-4.41</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-8.144</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-16.861</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-48.582</v>
       </c>
     </row>
     <row r="125">
@@ -3999,19 +3999,19 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-4.41</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-8.144</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-16.861</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-48.582</v>
       </c>
     </row>
     <row r="126">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -10538,7 +10538,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -10740,7 +10744,11 @@
           <t>Repayment of bank indebtedness 12</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -11995,7 +12003,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -12246,7 +12258,11 @@
           <t>Repayment of bank indebtedness 13</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -13797,7 +13813,11 @@
           <t>Lease payments 13</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -14150,7 +14170,11 @@
           <t>Repayment of bank indebtedness 12</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -15358,7 +15382,11 @@
           <t>Lease payments 13</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -15660,7 +15688,11 @@
           <t>Repayment of bank indebtedness 12</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/INIK.xlsx
+++ b/output/pdf_financials_xlsx/INIK.xlsx
@@ -10948,7 +10948,11 @@
           <t>Additions to intangible assets 6</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -12513,7 +12517,11 @@
           <t>Additions to intangible assets 6</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -14425,7 +14433,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/INIK.xlsx
+++ b/output/pdf_financials_xlsx/INIK.xlsx
@@ -901,16 +901,16 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.053</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.091</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>0.213</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.372</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
@@ -1014,25 +1014,17 @@
       <c r="C20" s="3" t="n">
         <v>-0.418196</v>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>-0.227</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-19.093</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-53.901</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-23.085</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1113,16 +1105,16 @@
         <v>-0.418196</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-0.174</v>
+        <v>-0.227</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-19.184</v>
+        <v>-19.093</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-54.114</v>
+        <v>-53.901</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>-22.713</v>
+        <v>-23.085</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1218,7 +1210,7 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>159.866667</v>
+        <v>159.108333</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1373,16 +1365,16 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-30.45977011494253</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.4743536280233528</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.3936134826477437</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.637828556333377</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -1407,16 +1399,16 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-1.695080370189966</v>
+        <v>-2.211397954213346</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-16.80934397644729</v>
+        <v>-16.72960824344809</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>-38.5430095655952</v>
+        <v>-38.3912990833268</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-12.68315836497655</v>
+        <v>-12.89088675452312</v>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
@@ -2168,13 +2160,13 @@
         <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>86.90600000000001</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>142.928</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>94.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2224,13 +2216,13 @@
         <v>99.479</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>3.766</v>
+        <v>90.672</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>6.628</v>
+        <v>149.556</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.6889999999999999</v>
+        <v>94.70099999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2306,19 +2298,19 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>3.303</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>7.606</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>25.014</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>43.494</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="65">
@@ -2384,25 +2376,25 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.013588</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.057161</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.863</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>8.438000000000001</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>9.275</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>11.456</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="68">
@@ -2424,13 +2416,13 @@
         <v>17.044</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>34.289</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>54.95</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="69">
@@ -2620,13 +2612,13 @@
         <v>9.619</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>51.938</v>
+        <v>17.649</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>79.111</v>
+        <v>24.161</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>153.051</v>
+        <v>117.711</v>
       </c>
     </row>
     <row r="76">
@@ -3269,16 +3261,16 @@
         <v>-0.418196</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>-0.174</v>
+        <v>-0.227</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-19.184</v>
+        <v>-19.093</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-54.114</v>
+        <v>-53.901</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-22.713</v>
+        <v>-23.085</v>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
@@ -4133,15 +4125,11 @@
       <c r="F129" s="3" t="n">
         <v>12.805</v>
       </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G129" s="3" t="n">
+        <v>14.127</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>-37.987</v>
       </c>
     </row>
     <row r="130">
@@ -4303,17 +4291,13 @@
         <v>6.906</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>8.404</v>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.218</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>7.694</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>34.22</v>
       </c>
     </row>
   </sheetData>
@@ -4862,7 +4846,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -9905,7 +9889,11 @@
           <t>Deferred tax expense (recovery) 23</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -10491,7 +10479,11 @@
           <t>Net cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -11664,7 +11656,11 @@
           <t>Deferred tax recovery 23</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -13325,7 +13321,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -15755,7 +15755,11 @@
           <t>Proceeds from share issuance 20</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -19935,7 +19939,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E310" t="inlineStr">
         <is>
           <t>-</t>
@@ -20590,7 +20598,11 @@
           <t>Income tax recovery (expense) 28</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
